--- a/IM/202602_HL_Maintain_Report.xlsx
+++ b/IM/202602_HL_Maintain_Report.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1113">
   <si>
-    <t>萊爾富 工作統計表  篩選月份：202602   (  製表日期:2026-02-26  )</t>
+    <t>萊爾富 工作統計表  篩選月份：202602   (  製表日期:2026-03-02  )</t>
   </si>
   <si>
     <t>項次</t>
